--- a/data/nzd0599/nzd0599.xlsx
+++ b/data/nzd0599/nzd0599.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L667"/>
+  <dimension ref="A1:L670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28440,6 +28440,132 @@
       <c r="L667" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>178.77</v>
+      </c>
+      <c r="C668" t="n">
+        <v>166.79</v>
+      </c>
+      <c r="D668" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="E668" t="n">
+        <v>180.13</v>
+      </c>
+      <c r="F668" t="n">
+        <v>182.84</v>
+      </c>
+      <c r="G668" t="n">
+        <v>186.55</v>
+      </c>
+      <c r="H668" t="n">
+        <v>185.15</v>
+      </c>
+      <c r="I668" t="n">
+        <v>182.01</v>
+      </c>
+      <c r="J668" t="n">
+        <v>186.28</v>
+      </c>
+      <c r="K668" t="n">
+        <v>191.87</v>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:12:13+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>178.71</v>
+      </c>
+      <c r="C669" t="n">
+        <v>166.43</v>
+      </c>
+      <c r="D669" t="n">
+        <v>175.38</v>
+      </c>
+      <c r="E669" t="n">
+        <v>180</v>
+      </c>
+      <c r="F669" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="G669" t="n">
+        <v>186.36</v>
+      </c>
+      <c r="H669" t="n">
+        <v>184.86</v>
+      </c>
+      <c r="I669" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="J669" t="n">
+        <v>185.73</v>
+      </c>
+      <c r="K669" t="n">
+        <v>191.74</v>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="C670" t="n">
+        <v>166.71</v>
+      </c>
+      <c r="D670" t="n">
+        <v>175.27</v>
+      </c>
+      <c r="E670" t="n">
+        <v>180.17</v>
+      </c>
+      <c r="F670" t="n">
+        <v>182.95</v>
+      </c>
+      <c r="G670" t="n">
+        <v>186.56</v>
+      </c>
+      <c r="H670" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="I670" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="J670" t="n">
+        <v>185.71</v>
+      </c>
+      <c r="K670" t="n">
+        <v>192.33</v>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B684"/>
+  <dimension ref="A1:B687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35297,6 +35423,36 @@
       </c>
       <c r="B684" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>
@@ -35459,28 +35615,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2714142619257351</v>
+        <v>0.2658988426176012</v>
       </c>
       <c r="J2" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="K2" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1122043694289743</v>
+        <v>0.1086369393542048</v>
       </c>
       <c r="M2" t="n">
-        <v>4.51779529238712</v>
+        <v>4.525740070535918</v>
       </c>
       <c r="N2" t="n">
-        <v>32.44591446297944</v>
+        <v>32.47096942753615</v>
       </c>
       <c r="O2" t="n">
-        <v>5.696131534908533</v>
+        <v>5.698330407017143</v>
       </c>
       <c r="P2" t="n">
-        <v>178.1038681020385</v>
+        <v>178.1617465769196</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35531,28 +35687,28 @@
         <v>0.0997</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3623279330359341</v>
+        <v>0.3555530357524888</v>
       </c>
       <c r="J3" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="K3" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2486906813503884</v>
+        <v>0.241422114054239</v>
       </c>
       <c r="M3" t="n">
-        <v>3.741900583380177</v>
+        <v>3.760452451879378</v>
       </c>
       <c r="N3" t="n">
-        <v>22.07772665731507</v>
+        <v>22.23397749125085</v>
       </c>
       <c r="O3" t="n">
-        <v>4.698694143835612</v>
+        <v>4.715291877630785</v>
       </c>
       <c r="P3" t="n">
-        <v>164.5801341605114</v>
+        <v>164.6512361177688</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35603,28 +35759,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6151296149977695</v>
+        <v>0.6133454774787312</v>
       </c>
       <c r="J4" t="n">
+        <v>669</v>
+      </c>
+      <c r="K4" t="n">
         <v>666</v>
       </c>
-      <c r="K4" t="n">
-        <v>663</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6573151260572392</v>
+        <v>0.6578945983738285</v>
       </c>
       <c r="M4" t="n">
-        <v>2.677991894331105</v>
+        <v>2.675143479389575</v>
       </c>
       <c r="N4" t="n">
-        <v>11.0120707147215</v>
+        <v>10.98025967114783</v>
       </c>
       <c r="O4" t="n">
-        <v>3.318444020127731</v>
+        <v>3.313647487459676</v>
       </c>
       <c r="P4" t="n">
-        <v>160.8874985832484</v>
+        <v>160.90620308363</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35675,28 +35831,28 @@
         <v>0.1166</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6172062945245627</v>
+        <v>0.6169173100427462</v>
       </c>
       <c r="J5" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="K5" t="n">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7132754721328496</v>
+        <v>0.7151155378924372</v>
       </c>
       <c r="M5" t="n">
-        <v>2.305221778747818</v>
+        <v>2.296372064414055</v>
       </c>
       <c r="N5" t="n">
-        <v>8.536340599760047</v>
+        <v>8.498435731806586</v>
       </c>
       <c r="O5" t="n">
-        <v>2.921701661662266</v>
+        <v>2.915207665297034</v>
       </c>
       <c r="P5" t="n">
-        <v>163.9806334102126</v>
+        <v>163.9836647966172</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35747,28 +35903,28 @@
         <v>0.1228</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4924837708890062</v>
+        <v>0.4931367243316626</v>
       </c>
       <c r="J6" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="K6" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6453616309000314</v>
+        <v>0.6481803800620487</v>
       </c>
       <c r="M6" t="n">
-        <v>2.232659285949389</v>
+        <v>2.22587393086988</v>
       </c>
       <c r="N6" t="n">
-        <v>7.419213732323835</v>
+        <v>7.388293104214288</v>
       </c>
       <c r="O6" t="n">
-        <v>2.723823366579381</v>
+        <v>2.718141479800911</v>
       </c>
       <c r="P6" t="n">
-        <v>168.9892267917382</v>
+        <v>168.9823739157066</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35819,28 +35975,28 @@
         <v>0.1034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4301473140351292</v>
+        <v>0.4298823734415643</v>
       </c>
       <c r="J7" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="K7" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6042571842227988</v>
+        <v>0.6063396772699918</v>
       </c>
       <c r="M7" t="n">
-        <v>2.130570997379527</v>
+        <v>2.122424592567018</v>
       </c>
       <c r="N7" t="n">
-        <v>6.745545926013944</v>
+        <v>6.715682909205616</v>
       </c>
       <c r="O7" t="n">
-        <v>2.597218882961916</v>
+        <v>2.591463468622627</v>
       </c>
       <c r="P7" t="n">
-        <v>175.3229761182978</v>
+        <v>175.3257568776393</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35891,28 +36047,28 @@
         <v>0.1267</v>
       </c>
       <c r="I8" t="n">
-        <v>0.108401404613201</v>
+        <v>0.1068382015209728</v>
       </c>
       <c r="J8" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="K8" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08675982897733681</v>
+        <v>0.08510808091229227</v>
       </c>
       <c r="M8" t="n">
-        <v>2.04028422230346</v>
+        <v>2.038714713914693</v>
       </c>
       <c r="N8" t="n">
-        <v>6.885374938329581</v>
+        <v>6.86811219895397</v>
       </c>
       <c r="O8" t="n">
-        <v>2.623999797699989</v>
+        <v>2.620708339162138</v>
       </c>
       <c r="P8" t="n">
-        <v>183.9006459456204</v>
+        <v>183.9170518946148</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35963,28 +36119,28 @@
         <v>0.1005</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.047077495321161</v>
+        <v>-0.0504861361180451</v>
       </c>
       <c r="J9" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="K9" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008680494948747008</v>
+        <v>0.01002361404861696</v>
       </c>
       <c r="M9" t="n">
-        <v>3.042738589552388</v>
+        <v>3.046612028220329</v>
       </c>
       <c r="N9" t="n">
-        <v>14.0892318605784</v>
+        <v>14.09061721995234</v>
       </c>
       <c r="O9" t="n">
-        <v>3.753562555836575</v>
+        <v>3.753747090568615</v>
       </c>
       <c r="P9" t="n">
-        <v>187.0791580668103</v>
+        <v>187.1149307887328</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36035,28 +36191,28 @@
         <v>0.1107</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1246568512696773</v>
+        <v>-0.1239793835144021</v>
       </c>
       <c r="J10" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="K10" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07243438004182423</v>
+        <v>0.0723559233350044</v>
       </c>
       <c r="M10" t="n">
-        <v>2.734586093662178</v>
+        <v>2.725583430060843</v>
       </c>
       <c r="N10" t="n">
-        <v>11.13188759205278</v>
+        <v>11.08484745342732</v>
       </c>
       <c r="O10" t="n">
-        <v>3.336448349975282</v>
+        <v>3.329391453918766</v>
       </c>
       <c r="P10" t="n">
-        <v>188.4648579422679</v>
+        <v>188.4577761295162</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36107,28 +36263,28 @@
         <v>0.1286</v>
       </c>
       <c r="I11" t="n">
-        <v>0.007107488127284013</v>
+        <v>0.006955488242079528</v>
       </c>
       <c r="J11" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="K11" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001600928862400819</v>
+        <v>0.0001548551425026856</v>
       </c>
       <c r="M11" t="n">
-        <v>3.370621037688823</v>
+        <v>3.356723430636591</v>
       </c>
       <c r="N11" t="n">
-        <v>17.64929366129777</v>
+        <v>17.57056963401152</v>
       </c>
       <c r="O11" t="n">
-        <v>4.20110624256252</v>
+        <v>4.191726331001527</v>
       </c>
       <c r="P11" t="n">
-        <v>191.9640526347603</v>
+        <v>191.9656403666196</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36166,7 +36322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L667"/>
+  <dimension ref="A1:L670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77479,6 +77635,192 @@
         </is>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>-36.81950582842412,174.806592326931</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>-36.82017172338607,174.8069608902275</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>-36.82074239976719,174.8075021738564</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>-36.821340237605796,174.80802116820007</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>-36.82193071772317,174.80853655628235</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>-36.8225165610215,174.80906013127512</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>-36.823128751839484,174.80953835310837</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>-36.82374363506374,174.810007876158</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>-36.82432078006358,174.81054912467732</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>-36.82487903344911,174.81113927168272</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:12:13+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>-36.819506119036255,174.8065917597901</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>-36.820173465741746,174.80695748630993</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>-36.8207415169556,174.80750399869055</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>-36.8213408777802,174.80801994780072</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>-36.82193116092455,174.80853571138726</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>-36.822517493277786,174.80905834484957</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>-36.823130205582665,174.80953565171353</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>-36.82374418648771,174.81000685148655</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>-36.82432356113213,174.8105440213496</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>-36.824879806786846,174.81113817702885</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>-36.81949996774549,174.80660376427082</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>-36.82017211057622,174.8069601338014</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>-36.82074202805704,174.8075029422076</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>-36.82134004062907,174.80802154370755</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>-36.821930176032566,174.8085375889319</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>-36.82251651195538,174.80906022529751</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>-36.82312900248486,174.80953788735061</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>-36.82374318389868,174.81000871452554</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>-36.82432366226189,174.81054383577404</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>-36.82487629702318,174.81114314507326</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0599/nzd0599.xlsx
+++ b/data/nzd0599/nzd0599.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L670"/>
+  <dimension ref="A1:L672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28564,6 +28564,90 @@
         <v>192.33</v>
       </c>
       <c r="L670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>179.43</v>
+      </c>
+      <c r="C671" t="n">
+        <v>166.64</v>
+      </c>
+      <c r="D671" t="n">
+        <v>175.22</v>
+      </c>
+      <c r="E671" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="F671" t="n">
+        <v>182.96</v>
+      </c>
+      <c r="G671" t="n">
+        <v>186.55</v>
+      </c>
+      <c r="H671" t="n">
+        <v>185.03</v>
+      </c>
+      <c r="I671" t="n">
+        <v>181.77</v>
+      </c>
+      <c r="J671" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="K671" t="n">
+        <v>192</v>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:59+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>179.43</v>
+      </c>
+      <c r="C672" t="n">
+        <v>166.64</v>
+      </c>
+      <c r="D672" t="n">
+        <v>175.22</v>
+      </c>
+      <c r="E672" t="n">
+        <v>180.86</v>
+      </c>
+      <c r="F672" t="n">
+        <v>183.52</v>
+      </c>
+      <c r="G672" t="n">
+        <v>187.34</v>
+      </c>
+      <c r="H672" t="n">
+        <v>185.94</v>
+      </c>
+      <c r="I672" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="J672" t="n">
+        <v>186.02</v>
+      </c>
+      <c r="K672" t="n">
+        <v>192.22</v>
+      </c>
+      <c r="L672" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28580,7 +28664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B687"/>
+  <dimension ref="A1:B689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35453,6 +35537,26 @@
       </c>
       <c r="B687" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>-0.88</v>
       </c>
     </row>
   </sheetData>
@@ -35615,28 +35719,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2658988426176012</v>
+        <v>0.26243962969447</v>
       </c>
       <c r="J2" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K2" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1086369393542048</v>
+        <v>0.1064641844827174</v>
       </c>
       <c r="M2" t="n">
-        <v>4.525740070535918</v>
+        <v>4.529963568541638</v>
       </c>
       <c r="N2" t="n">
-        <v>32.47096942753615</v>
+        <v>32.47469604875857</v>
       </c>
       <c r="O2" t="n">
-        <v>5.698330407017143</v>
+        <v>5.698657390013771</v>
       </c>
       <c r="P2" t="n">
-        <v>178.1617465769196</v>
+        <v>178.1981632978321</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35687,28 +35791,28 @@
         <v>0.0997</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3555530357524888</v>
+        <v>0.3511001530576159</v>
       </c>
       <c r="J3" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K3" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L3" t="n">
-        <v>0.241422114054239</v>
+        <v>0.2366844770469938</v>
       </c>
       <c r="M3" t="n">
-        <v>3.760452451879378</v>
+        <v>3.772645703735505</v>
       </c>
       <c r="N3" t="n">
-        <v>22.23397749125085</v>
+        <v>22.33439462610627</v>
       </c>
       <c r="O3" t="n">
-        <v>4.715291877630785</v>
+        <v>4.725927911649338</v>
       </c>
       <c r="P3" t="n">
-        <v>164.6512361177688</v>
+        <v>164.6981136575844</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35759,28 +35863,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6133454774787312</v>
+        <v>0.6121128430110612</v>
       </c>
       <c r="J4" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K4" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6578945983738285</v>
+        <v>0.6582223311774101</v>
       </c>
       <c r="M4" t="n">
-        <v>2.675143479389575</v>
+        <v>2.673440753428912</v>
       </c>
       <c r="N4" t="n">
-        <v>10.98025967114783</v>
+        <v>10.96021189426252</v>
       </c>
       <c r="O4" t="n">
-        <v>3.313647487459676</v>
+        <v>3.310621073796052</v>
       </c>
       <c r="P4" t="n">
-        <v>160.90620308363</v>
+        <v>160.9191663865157</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35831,28 +35935,28 @@
         <v>0.1166</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6169173100427462</v>
+        <v>0.6169002905603803</v>
       </c>
       <c r="J5" t="n">
+        <v>671</v>
+      </c>
+      <c r="K5" t="n">
         <v>669</v>
       </c>
-      <c r="K5" t="n">
-        <v>667</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.7151155378924372</v>
+        <v>0.7164461511728692</v>
       </c>
       <c r="M5" t="n">
-        <v>2.296372064414055</v>
+        <v>2.290719440092196</v>
       </c>
       <c r="N5" t="n">
-        <v>8.498435731806586</v>
+        <v>8.473520713518809</v>
       </c>
       <c r="O5" t="n">
-        <v>2.915207665297034</v>
+        <v>2.910931245068974</v>
       </c>
       <c r="P5" t="n">
-        <v>163.9836647966172</v>
+        <v>163.9838416511623</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35903,28 +36007,28 @@
         <v>0.1228</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4931367243316626</v>
+        <v>0.4937800248778772</v>
       </c>
       <c r="J6" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K6" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6481803800620487</v>
+        <v>0.6501759478245752</v>
       </c>
       <c r="M6" t="n">
-        <v>2.22587393086988</v>
+        <v>2.222391866250918</v>
       </c>
       <c r="N6" t="n">
-        <v>7.388293104214288</v>
+        <v>7.369934535946668</v>
       </c>
       <c r="O6" t="n">
-        <v>2.718141479800911</v>
+        <v>2.714762335075884</v>
       </c>
       <c r="P6" t="n">
-        <v>168.9823739157066</v>
+        <v>168.975600116082</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35975,28 +36079,28 @@
         <v>0.1034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4298823734415643</v>
+        <v>0.4299613194940434</v>
       </c>
       <c r="J7" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K7" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6063396772699918</v>
+        <v>0.6079971914930988</v>
       </c>
       <c r="M7" t="n">
-        <v>2.122424592567018</v>
+        <v>2.117218407093971</v>
       </c>
       <c r="N7" t="n">
-        <v>6.715682909205616</v>
+        <v>6.696135118356331</v>
       </c>
       <c r="O7" t="n">
-        <v>2.591463468622627</v>
+        <v>2.587689146392266</v>
       </c>
       <c r="P7" t="n">
-        <v>175.3257568776393</v>
+        <v>175.3249236507654</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36047,28 +36151,28 @@
         <v>0.1267</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1068382015209728</v>
+        <v>0.106075846025778</v>
       </c>
       <c r="J8" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K8" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08510808091229227</v>
+        <v>0.08445092136630261</v>
       </c>
       <c r="M8" t="n">
-        <v>2.038714713914693</v>
+        <v>2.036325811444334</v>
       </c>
       <c r="N8" t="n">
-        <v>6.86811219895397</v>
+        <v>6.85311587965184</v>
       </c>
       <c r="O8" t="n">
-        <v>2.620708339162138</v>
+        <v>2.617845656193627</v>
       </c>
       <c r="P8" t="n">
-        <v>183.9170518946148</v>
+        <v>183.9250750697071</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36119,28 +36223,28 @@
         <v>0.1005</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0504861361180451</v>
+        <v>-0.05263675959312517</v>
       </c>
       <c r="J9" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K9" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01002361404861696</v>
+        <v>0.01092794951713583</v>
       </c>
       <c r="M9" t="n">
-        <v>3.046612028220329</v>
+        <v>3.04852175168054</v>
       </c>
       <c r="N9" t="n">
-        <v>14.09061721995234</v>
+        <v>14.08787111307585</v>
       </c>
       <c r="O9" t="n">
-        <v>3.753747090568615</v>
+        <v>3.75338129065991</v>
       </c>
       <c r="P9" t="n">
-        <v>187.1149307887328</v>
+        <v>187.1375693699526</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36191,28 +36295,28 @@
         <v>0.1107</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1239793835144021</v>
+        <v>-0.1236754443367012</v>
       </c>
       <c r="J10" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K10" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0723559233350044</v>
+        <v>0.07246512874647226</v>
       </c>
       <c r="M10" t="n">
-        <v>2.725583430060843</v>
+        <v>2.718904888027586</v>
       </c>
       <c r="N10" t="n">
-        <v>11.08484745342732</v>
+        <v>11.05298570149725</v>
       </c>
       <c r="O10" t="n">
-        <v>3.329391453918766</v>
+        <v>3.324603089317166</v>
       </c>
       <c r="P10" t="n">
-        <v>188.4577761295162</v>
+        <v>188.4545858223165</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36263,28 +36367,28 @@
         <v>0.1286</v>
       </c>
       <c r="I11" t="n">
-        <v>0.006955488242079528</v>
+        <v>0.006931854747167056</v>
       </c>
       <c r="J11" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="K11" t="n">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001548551425026856</v>
+        <v>0.0001548291261213031</v>
       </c>
       <c r="M11" t="n">
-        <v>3.356723430636591</v>
+        <v>3.347035275840671</v>
       </c>
       <c r="N11" t="n">
-        <v>17.57056963401152</v>
+        <v>17.51823991459083</v>
       </c>
       <c r="O11" t="n">
-        <v>4.191726331001527</v>
+        <v>4.18547965167564</v>
       </c>
       <c r="P11" t="n">
-        <v>191.9656403666196</v>
+        <v>191.9658876727104</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36322,7 +36426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L670"/>
+  <dimension ref="A1:L672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77821,6 +77925,130 @@
         </is>
       </c>
     </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>-36.81950263169046,174.80659856548021</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>-36.82017244936761,174.8069594719285</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>-36.820742260375866,174.8075024619881</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>-36.821340779291845,174.80802013555444</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>-36.821930126787976,174.80853768280912</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>-36.8225165610215,174.80906013127512</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>-36.82312935338838,174.8095372352898</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>-36.82374483817055,174.81000564051115</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>-36.824325735421944,174.810540031475</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>-36.824878260111355,174.8111403663366</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:59+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>-36.81950263169046,174.80659856548021</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>-36.82017244936761,174.8069594719285</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>-36.820742260375866,174.8075024619881</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>-36.82133664278006,174.8080280212115</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>-36.821927369090275,174.8085429399338</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>-36.822512684797715,174.80906755904394</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>-36.82312479164225,174.80954571207997</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>-36.82374117872055,174.81001244060346</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>-36.824322094750556,174.8105467121952</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>-36.82487695138592,174.8111422188277</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0599/nzd0599.xlsx
+++ b/data/nzd0599/nzd0599.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L672"/>
+  <dimension ref="A1:L678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28648,6 +28648,258 @@
         <v>192.22</v>
       </c>
       <c r="L672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>179.61</v>
+      </c>
+      <c r="C673" t="n">
+        <v>167.2</v>
+      </c>
+      <c r="D673" t="n">
+        <v>175.38</v>
+      </c>
+      <c r="E673" t="n">
+        <v>181.16</v>
+      </c>
+      <c r="F673" t="n">
+        <v>183.89</v>
+      </c>
+      <c r="G673" t="n">
+        <v>187.63</v>
+      </c>
+      <c r="H673" t="n">
+        <v>186.13</v>
+      </c>
+      <c r="I673" t="n">
+        <v>182.82</v>
+      </c>
+      <c r="J673" t="n">
+        <v>185.66</v>
+      </c>
+      <c r="K673" t="n">
+        <v>192.48</v>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>178.92</v>
+      </c>
+      <c r="C674" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="D674" t="n">
+        <v>175.44</v>
+      </c>
+      <c r="E674" t="n">
+        <v>180.99</v>
+      </c>
+      <c r="F674" t="n">
+        <v>184.13</v>
+      </c>
+      <c r="G674" t="n">
+        <v>187.43</v>
+      </c>
+      <c r="H674" t="n">
+        <v>186.16</v>
+      </c>
+      <c r="I674" t="n">
+        <v>182.98</v>
+      </c>
+      <c r="J674" t="n">
+        <v>185.58</v>
+      </c>
+      <c r="K674" t="n">
+        <v>192.26</v>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:28+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>178.98</v>
+      </c>
+      <c r="C675" t="n">
+        <v>167.84</v>
+      </c>
+      <c r="D675" t="n">
+        <v>175.86</v>
+      </c>
+      <c r="E675" t="n">
+        <v>181.41</v>
+      </c>
+      <c r="F675" t="n">
+        <v>184.84</v>
+      </c>
+      <c r="G675" t="n">
+        <v>188.08</v>
+      </c>
+      <c r="H675" t="n">
+        <v>186.63</v>
+      </c>
+      <c r="I675" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="J675" t="n">
+        <v>186.29</v>
+      </c>
+      <c r="K675" t="n">
+        <v>192.31</v>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>178.58</v>
+      </c>
+      <c r="C676" t="n">
+        <v>168.09</v>
+      </c>
+      <c r="D676" t="n">
+        <v>175.97</v>
+      </c>
+      <c r="E676" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="F676" t="n">
+        <v>184.73</v>
+      </c>
+      <c r="G676" t="n">
+        <v>187.96</v>
+      </c>
+      <c r="H676" t="n">
+        <v>186.66</v>
+      </c>
+      <c r="I676" t="n">
+        <v>183.46</v>
+      </c>
+      <c r="J676" t="n">
+        <v>186.14</v>
+      </c>
+      <c r="K676" t="n">
+        <v>192.33</v>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>178.79</v>
+      </c>
+      <c r="C677" t="n">
+        <v>168.39</v>
+      </c>
+      <c r="D677" t="n">
+        <v>176.13</v>
+      </c>
+      <c r="E677" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="F677" t="n">
+        <v>184.73</v>
+      </c>
+      <c r="G677" t="n">
+        <v>187.96</v>
+      </c>
+      <c r="H677" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="I677" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="J677" t="n">
+        <v>186</v>
+      </c>
+      <c r="K677" t="n">
+        <v>192.35</v>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>178.79</v>
+      </c>
+      <c r="C678" t="n">
+        <v>170.4</v>
+      </c>
+      <c r="D678" t="n">
+        <v>178.46</v>
+      </c>
+      <c r="E678" t="n">
+        <v>183.52</v>
+      </c>
+      <c r="F678" t="n">
+        <v>186.17</v>
+      </c>
+      <c r="G678" t="n">
+        <v>188.75</v>
+      </c>
+      <c r="H678" t="n">
+        <v>186.62</v>
+      </c>
+      <c r="I678" t="n">
+        <v>183.98</v>
+      </c>
+      <c r="J678" t="n">
+        <v>186.43</v>
+      </c>
+      <c r="K678" t="n">
+        <v>194.48</v>
+      </c>
+      <c r="L678" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28664,7 +28916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B689"/>
+  <dimension ref="A1:B695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35557,6 +35809,66 @@
       </c>
       <c r="B689" t="n">
         <v>-0.88</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -35719,28 +36031,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.26243962969447</v>
+        <v>0.2514815670958064</v>
       </c>
       <c r="J2" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="K2" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1064641844827174</v>
+        <v>0.09944024085067249</v>
       </c>
       <c r="M2" t="n">
-        <v>4.529963568541638</v>
+        <v>4.545470883830598</v>
       </c>
       <c r="N2" t="n">
-        <v>32.47469604875857</v>
+        <v>32.52851878127122</v>
       </c>
       <c r="O2" t="n">
-        <v>5.698657390013771</v>
+        <v>5.703377839602704</v>
       </c>
       <c r="P2" t="n">
-        <v>178.1981632978321</v>
+        <v>178.3139757068449</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35791,28 +36103,28 @@
         <v>0.0997</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3511001530576159</v>
+        <v>0.3408686883124366</v>
       </c>
       <c r="J3" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="K3" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2366844770469938</v>
+        <v>0.2272194939885573</v>
       </c>
       <c r="M3" t="n">
-        <v>3.772645703735505</v>
+        <v>3.792878998573909</v>
       </c>
       <c r="N3" t="n">
-        <v>22.33439462610627</v>
+        <v>22.4432832692253</v>
       </c>
       <c r="O3" t="n">
-        <v>4.725927911649338</v>
+        <v>4.737434249593898</v>
       </c>
       <c r="P3" t="n">
-        <v>164.6981136575844</v>
+        <v>164.8062194114665</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35863,28 +36175,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6121128430110612</v>
+        <v>0.6101598276439069</v>
       </c>
       <c r="J4" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="K4" t="n">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6582223311774101</v>
+        <v>0.6608070454323942</v>
       </c>
       <c r="M4" t="n">
-        <v>2.673440753428912</v>
+        <v>2.662862012360768</v>
       </c>
       <c r="N4" t="n">
-        <v>10.96021189426252</v>
+        <v>10.88301116878049</v>
       </c>
       <c r="O4" t="n">
-        <v>3.310621073796052</v>
+        <v>3.298940916230615</v>
       </c>
       <c r="P4" t="n">
-        <v>160.9191663865157</v>
+        <v>160.9397656877821</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35935,28 +36247,28 @@
         <v>0.1166</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6169002905603803</v>
+        <v>0.6188733643037716</v>
       </c>
       <c r="J5" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="K5" t="n">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7164461511728692</v>
+        <v>0.7213197619518578</v>
       </c>
       <c r="M5" t="n">
-        <v>2.290719440092196</v>
+        <v>2.279772078860162</v>
       </c>
       <c r="N5" t="n">
-        <v>8.473520713518809</v>
+        <v>8.415466747965983</v>
       </c>
       <c r="O5" t="n">
-        <v>2.910931245068974</v>
+        <v>2.900942389632373</v>
       </c>
       <c r="P5" t="n">
-        <v>163.9838416511623</v>
+        <v>163.9629860693611</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36007,28 +36319,28 @@
         <v>0.1228</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4937800248778772</v>
+        <v>0.4981963844916433</v>
       </c>
       <c r="J6" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="K6" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6501759478245752</v>
+        <v>0.6568422021249477</v>
       </c>
       <c r="M6" t="n">
-        <v>2.222391866250918</v>
+        <v>2.224006653223458</v>
       </c>
       <c r="N6" t="n">
-        <v>7.369934535946668</v>
+        <v>7.364369471638737</v>
       </c>
       <c r="O6" t="n">
-        <v>2.714762335075884</v>
+        <v>2.713737178069891</v>
       </c>
       <c r="P6" t="n">
-        <v>168.975600116082</v>
+        <v>168.9289124871505</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36079,28 +36391,28 @@
         <v>0.1034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4299613194940434</v>
+        <v>0.4319078583596001</v>
       </c>
       <c r="J7" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="K7" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6079971914930988</v>
+        <v>0.6144111510882422</v>
       </c>
       <c r="M7" t="n">
-        <v>2.117218407093971</v>
+        <v>2.107515517606868</v>
       </c>
       <c r="N7" t="n">
-        <v>6.696135118356331</v>
+        <v>6.648890654142738</v>
       </c>
       <c r="O7" t="n">
-        <v>2.587689146392266</v>
+        <v>2.578544289738444</v>
       </c>
       <c r="P7" t="n">
-        <v>175.3249236507654</v>
+        <v>175.3043444461754</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36151,28 +36463,28 @@
         <v>0.1267</v>
       </c>
       <c r="I8" t="n">
-        <v>0.106075846025778</v>
+        <v>0.1055801834892577</v>
       </c>
       <c r="J8" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="K8" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08445092136630261</v>
+        <v>0.08524669725501433</v>
       </c>
       <c r="M8" t="n">
-        <v>2.036325811444334</v>
+        <v>2.020636633448614</v>
       </c>
       <c r="N8" t="n">
-        <v>6.85311587965184</v>
+        <v>6.793488607655098</v>
       </c>
       <c r="O8" t="n">
-        <v>2.617845656193627</v>
+        <v>2.606432160570288</v>
       </c>
       <c r="P8" t="n">
-        <v>183.9250750697071</v>
+        <v>183.9303083001576</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36223,28 +36535,28 @@
         <v>0.1005</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05263675959312517</v>
+        <v>-0.05673460117885371</v>
       </c>
       <c r="J9" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="K9" t="n">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01092794951713583</v>
+        <v>0.01287866130275672</v>
       </c>
       <c r="M9" t="n">
-        <v>3.04852175168054</v>
+        <v>3.042270643045187</v>
       </c>
       <c r="N9" t="n">
-        <v>14.08787111307585</v>
+        <v>14.01191303936776</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75338129065991</v>
+        <v>3.743248995106758</v>
       </c>
       <c r="P9" t="n">
-        <v>187.1375693699526</v>
+        <v>187.180866606728</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36295,28 +36607,28 @@
         <v>0.1107</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1236754443367012</v>
+        <v>-0.1221506593151213</v>
       </c>
       <c r="J10" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="K10" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07246512874647226</v>
+        <v>0.07207965773974145</v>
       </c>
       <c r="M10" t="n">
-        <v>2.718904888027586</v>
+        <v>2.701996203956204</v>
       </c>
       <c r="N10" t="n">
-        <v>11.05298570149725</v>
+        <v>10.9625424619807</v>
       </c>
       <c r="O10" t="n">
-        <v>3.324603089317166</v>
+        <v>3.310973038546327</v>
       </c>
       <c r="P10" t="n">
-        <v>188.4545858223165</v>
+        <v>188.4385226031132</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36367,28 +36679,28 @@
         <v>0.1286</v>
       </c>
       <c r="I11" t="n">
-        <v>0.006931854747167056</v>
+        <v>0.007891358175598247</v>
       </c>
       <c r="J11" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="K11" t="n">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001548291261213031</v>
+        <v>0.0002045526758359673</v>
       </c>
       <c r="M11" t="n">
-        <v>3.347035275840671</v>
+        <v>3.32268575984974</v>
       </c>
       <c r="N11" t="n">
-        <v>17.51823991459083</v>
+        <v>17.37125434181458</v>
       </c>
       <c r="O11" t="n">
-        <v>4.18547965167564</v>
+        <v>4.167883676617497</v>
       </c>
       <c r="P11" t="n">
-        <v>191.9658876727104</v>
+        <v>191.9557721709909</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36426,7 +36738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L672"/>
+  <dimension ref="A1:L678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78049,6 +78361,378 @@
         </is>
       </c>
     </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>-36.81950175985394,174.80660026690265</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>-36.82016973903644,174.80696476691116</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>-36.8207415169556,174.80750399869055</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>-36.8213351654543,174.80803083751738</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>-36.8219255470399,174.80854641339099</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>-36.82251126188,174.80907028569308</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>-36.823123839189684,174.8095474819591</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>-36.82373957457797,174.81001542146564</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>-36.824323915086296,174.81054337183517</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>-36.824875404710355,174.8111444081353</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>-36.819505101893775,174.80659374478313</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>-36.8201682870732,174.80696760350884</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>-36.82074123817299,174.80750457495395</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>-36.82133600260557,174.8080292416107</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>-36.82192436516934,174.80854866644418</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>-36.82251224320257,174.80906840524543</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>-36.82312368880245,174.8095477614137</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>-36.82373877250665,174.8100169118967</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>-36.824324319605346,174.8105426295329</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>-36.82487671343582,174.81114255564427</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:28+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>-36.81950481128164,174.806594311924</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>-36.82016664151481,174.8069708183194</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>-36.82073928669463,174.8075086087977</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>-36.82133393434945,174.80803318443887</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>-36.82192086880198,174.8085553317262</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>-36.82250905390413,174.80907451670015</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>-36.823121332735454,174.80955213953553</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>-36.823736667069355,174.810020824278</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>-36.8243207294987,174.81054921746508</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>-36.824876415998226,174.81114297666497</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>-36.819506748695886,174.8065905309849</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>-36.82016543154534,174.8069731821506</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>-36.820738775593156,174.80750966528055</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>-36.82133398359365,174.808033090562</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>-36.82192141049273,174.80855429907692</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>-36.8225096426977,174.8090733884316</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>-36.823121182348196,174.8095524189901</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>-36.82373636629259,174.81002138318962</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>-36.82432148797196,174.81054782564848</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>-36.82487629702318,174.81114314507326</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>-36.81950573155342,174.80659251597794</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>-36.82016397958191,174.806976018748</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>-36.820738032172784,174.80751120198286</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>-36.82133373737266,174.8080335599463</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>-36.82192141049273,174.80855429907692</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>-36.8225096426977,174.8090733884316</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>-36.82312098183186,174.80955279159622</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>-36.82373566448013,174.81002268731666</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>-36.82432219588032,174.81054652661962</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>-36.82487617804814,174.8111433134815</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>-36.81950573155342,174.80659251597794</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>-36.82015425142532,174.80699502394748</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>-36.820727206111485,174.80753358020678</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>-36.82132354382277,174.80805299245313</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>-36.82191431926781,174.80856781739368</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>-36.82250576647312,174.8090808161991</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>-36.82312138286454,174.80955204638403</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>-36.82373375956051,174.81002622708996</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>-36.8243200215903,174.8105505164939</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>-36.82486350720476,174.81116124896</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0599/nzd0599.xlsx
+++ b/data/nzd0599/nzd0599.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L678"/>
+  <dimension ref="A1:L682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28888,7 +28888,7 @@
         <v>188.75</v>
       </c>
       <c r="H678" t="n">
-        <v>186.62</v>
+        <v>188.88</v>
       </c>
       <c r="I678" t="n">
         <v>183.98</v>
@@ -28900,6 +28900,174 @@
         <v>194.48</v>
       </c>
       <c r="L678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>177.7</v>
+      </c>
+      <c r="C679" t="n">
+        <v>171.57</v>
+      </c>
+      <c r="D679" t="n">
+        <v>179.51</v>
+      </c>
+      <c r="E679" t="n">
+        <v>184.34</v>
+      </c>
+      <c r="F679" t="n">
+        <v>187.07</v>
+      </c>
+      <c r="G679" t="n">
+        <v>189.59</v>
+      </c>
+      <c r="H679" t="n">
+        <v>189.85</v>
+      </c>
+      <c r="I679" t="n">
+        <v>185.21</v>
+      </c>
+      <c r="J679" t="n">
+        <v>186.57</v>
+      </c>
+      <c r="K679" t="n">
+        <v>195.91</v>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>177.7</v>
+      </c>
+      <c r="C680" t="n">
+        <v>173.49</v>
+      </c>
+      <c r="D680" t="n">
+        <v>181.52</v>
+      </c>
+      <c r="E680" t="n">
+        <v>186.14</v>
+      </c>
+      <c r="F680" t="n">
+        <v>189.13</v>
+      </c>
+      <c r="G680" t="n">
+        <v>191.23</v>
+      </c>
+      <c r="H680" t="n">
+        <v>192.14</v>
+      </c>
+      <c r="I680" t="n">
+        <v>185.21</v>
+      </c>
+      <c r="J680" t="n">
+        <v>186.57</v>
+      </c>
+      <c r="K680" t="n">
+        <v>197.84</v>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>177.7</v>
+      </c>
+      <c r="C681" t="n">
+        <v>173.49</v>
+      </c>
+      <c r="D681" t="n">
+        <v>180.84</v>
+      </c>
+      <c r="E681" t="n">
+        <v>185.45</v>
+      </c>
+      <c r="F681" t="n">
+        <v>188.35</v>
+      </c>
+      <c r="G681" t="n">
+        <v>191.77</v>
+      </c>
+      <c r="H681" t="n">
+        <v>192.59</v>
+      </c>
+      <c r="I681" t="n">
+        <v>184.69</v>
+      </c>
+      <c r="J681" t="n">
+        <v>185.47</v>
+      </c>
+      <c r="K681" t="n">
+        <v>196.89</v>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>177.74</v>
+      </c>
+      <c r="C682" t="n">
+        <v>173.35</v>
+      </c>
+      <c r="D682" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="E682" t="n">
+        <v>185.45</v>
+      </c>
+      <c r="F682" t="n">
+        <v>188.26</v>
+      </c>
+      <c r="G682" t="n">
+        <v>191.78</v>
+      </c>
+      <c r="H682" t="n">
+        <v>192.43</v>
+      </c>
+      <c r="I682" t="n">
+        <v>184.56</v>
+      </c>
+      <c r="J682" t="n">
+        <v>185.31</v>
+      </c>
+      <c r="K682" t="n">
+        <v>196.67</v>
+      </c>
+      <c r="L682" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28916,7 +29084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B695"/>
+  <dimension ref="A1:B699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35869,6 +36037,46 @@
       </c>
       <c r="B695" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -36031,28 +36239,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2514815670958064</v>
+        <v>0.2430043582692371</v>
       </c>
       <c r="J2" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K2" t="n">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09944024085067249</v>
+        <v>0.09375112111837458</v>
       </c>
       <c r="M2" t="n">
-        <v>4.545470883830598</v>
+        <v>4.561815068479111</v>
       </c>
       <c r="N2" t="n">
-        <v>32.52851878127122</v>
+        <v>32.65079651543233</v>
       </c>
       <c r="O2" t="n">
-        <v>5.703377839602704</v>
+        <v>5.7140875488071</v>
       </c>
       <c r="P2" t="n">
-        <v>178.3139757068449</v>
+        <v>178.4039507072486</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36103,28 +36311,28 @@
         <v>0.0997</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3408686883124366</v>
+        <v>0.3397145005283524</v>
       </c>
       <c r="J3" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K3" t="n">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2272194939885573</v>
+        <v>0.2282402721371442</v>
       </c>
       <c r="M3" t="n">
-        <v>3.792878998573909</v>
+        <v>3.776590326952249</v>
       </c>
       <c r="N3" t="n">
-        <v>22.4432832692253</v>
+        <v>22.3209486419019</v>
       </c>
       <c r="O3" t="n">
-        <v>4.737434249593898</v>
+        <v>4.724505121375349</v>
       </c>
       <c r="P3" t="n">
-        <v>164.8062194114665</v>
+        <v>164.8184658031829</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36175,28 +36383,28 @@
         <v>0.1029</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6101598276439069</v>
+        <v>0.6139044336705518</v>
       </c>
       <c r="J4" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K4" t="n">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6608070454323942</v>
+        <v>0.6651205214210241</v>
       </c>
       <c r="M4" t="n">
-        <v>2.662862012360768</v>
+        <v>2.666159531356081</v>
       </c>
       <c r="N4" t="n">
-        <v>10.88301116878049</v>
+        <v>10.88328193126382</v>
       </c>
       <c r="O4" t="n">
-        <v>3.298940916230615</v>
+        <v>3.298981953764497</v>
       </c>
       <c r="P4" t="n">
-        <v>160.9397656877821</v>
+        <v>160.9000596312998</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36247,28 +36455,28 @@
         <v>0.1166</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6188733643037716</v>
+        <v>0.6243090623438847</v>
       </c>
       <c r="J5" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K5" t="n">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7213197619518578</v>
+        <v>0.7243050437680946</v>
       </c>
       <c r="M5" t="n">
-        <v>2.279772078860162</v>
+        <v>2.292055611308478</v>
       </c>
       <c r="N5" t="n">
-        <v>8.415466747965983</v>
+        <v>8.497470191302691</v>
       </c>
       <c r="O5" t="n">
-        <v>2.900942389632373</v>
+        <v>2.915042056523832</v>
       </c>
       <c r="P5" t="n">
-        <v>163.9629860693611</v>
+        <v>163.9053201962167</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36319,28 +36527,28 @@
         <v>0.1228</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4981963844916433</v>
+        <v>0.5049452260870605</v>
       </c>
       <c r="J6" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K6" t="n">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6568422021249477</v>
+        <v>0.6597042897788987</v>
       </c>
       <c r="M6" t="n">
-        <v>2.224006653223458</v>
+        <v>2.243596754540853</v>
       </c>
       <c r="N6" t="n">
-        <v>7.364369471638737</v>
+        <v>7.522987669487161</v>
       </c>
       <c r="O6" t="n">
-        <v>2.713737178069891</v>
+        <v>2.742806531545228</v>
       </c>
       <c r="P6" t="n">
-        <v>168.9289124871505</v>
+        <v>168.8572808805732</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36391,28 +36599,28 @@
         <v>0.1034</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4319078583596001</v>
+        <v>0.4366991036487489</v>
       </c>
       <c r="J7" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K7" t="n">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6144111510882422</v>
+        <v>0.6189869160431192</v>
       </c>
       <c r="M7" t="n">
-        <v>2.107515517606868</v>
+        <v>2.117290626698605</v>
       </c>
       <c r="N7" t="n">
-        <v>6.648890654142738</v>
+        <v>6.714561623668231</v>
       </c>
       <c r="O7" t="n">
-        <v>2.578544289738444</v>
+        <v>2.591247117445233</v>
       </c>
       <c r="P7" t="n">
-        <v>175.3043444461754</v>
+        <v>175.2534851596931</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36463,28 +36671,28 @@
         <v>0.1267</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1055801834892577</v>
+        <v>0.1119550360047446</v>
       </c>
       <c r="J8" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K8" t="n">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08524669725501433</v>
+        <v>0.09400295347444343</v>
       </c>
       <c r="M8" t="n">
-        <v>2.020636633448614</v>
+        <v>2.042392445814423</v>
       </c>
       <c r="N8" t="n">
-        <v>6.793488607655098</v>
+        <v>6.909827306981914</v>
       </c>
       <c r="O8" t="n">
-        <v>2.606432160570288</v>
+        <v>2.628655037653651</v>
       </c>
       <c r="P8" t="n">
-        <v>183.9303083001576</v>
+        <v>183.862657916761</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36535,28 +36743,28 @@
         <v>0.1005</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05673460117885371</v>
+        <v>-0.05758351239439039</v>
       </c>
       <c r="J9" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K9" t="n">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01287866130275672</v>
+        <v>0.01342981005575006</v>
       </c>
       <c r="M9" t="n">
-        <v>3.042270643045187</v>
+        <v>3.028647670576408</v>
       </c>
       <c r="N9" t="n">
-        <v>14.01191303936776</v>
+        <v>13.93314204319538</v>
       </c>
       <c r="O9" t="n">
-        <v>3.743248995106758</v>
+        <v>3.732712424389987</v>
       </c>
       <c r="P9" t="n">
-        <v>187.180866606728</v>
+        <v>187.1898794722542</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36607,28 +36815,28 @@
         <v>0.1107</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1221506593151213</v>
+        <v>-0.1212000477045383</v>
       </c>
       <c r="J10" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K10" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07207965773974145</v>
+        <v>0.07186684608338934</v>
       </c>
       <c r="M10" t="n">
-        <v>2.701996203956204</v>
+        <v>2.690565659694339</v>
       </c>
       <c r="N10" t="n">
-        <v>10.9625424619807</v>
+        <v>10.9041844513863</v>
       </c>
       <c r="O10" t="n">
-        <v>3.310973038546327</v>
+        <v>3.30214845992519</v>
       </c>
       <c r="P10" t="n">
-        <v>188.4385226031132</v>
+        <v>188.4284739384887</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36679,28 +36887,28 @@
         <v>0.1286</v>
       </c>
       <c r="I11" t="n">
-        <v>0.007891358175598247</v>
+        <v>0.01322422444644462</v>
       </c>
       <c r="J11" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="K11" t="n">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002045526758359673</v>
+        <v>0.0005774588300971883</v>
       </c>
       <c r="M11" t="n">
-        <v>3.32268575984974</v>
+        <v>3.33277068457993</v>
       </c>
       <c r="N11" t="n">
-        <v>17.37125434181458</v>
+        <v>17.39700323844432</v>
       </c>
       <c r="O11" t="n">
-        <v>4.167883676617497</v>
+        <v>4.170971498157751</v>
       </c>
       <c r="P11" t="n">
-        <v>191.9557721709909</v>
+        <v>191.8993704078641</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36738,7 +36946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L678"/>
+  <dimension ref="A1:L682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78709,7 +78917,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>-36.82312138286454,174.80955204638403</t>
+          <t>-36.82311005368924,174.80957309862575</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -78728,6 +78936,254 @@
         </is>
       </c>
       <c r="L678" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>-36.819511011006824,174.80658221291824</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>-36.82014858876567,174.8070060866733</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>-36.820722327413,174.80754366481202</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>-36.82131950579732,174.80806069035293</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>-36.82190988725149,174.80857626634037</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>-36.82250164491737,174.8090887140776</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>-36.82310519116599,174.8095821343205</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>-36.82372759363578,174.81003768477603</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>-36.8243193136819,174.81055181552267</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>-36.824855000486885,174.81117329014643</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>-36.819511011006824,174.80658221291824</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>-36.82013929619381,174.80702424088645</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>-36.82071298818789,174.80756296962414</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>-36.82131064183736,174.80807758817892</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>-36.821899742856424,174.80859560503686</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>-36.82249359806899,174.8091041337427</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>-36.8230937115982,174.8096034660076</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>-36.82372759363578,174.81003768477603</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>-36.8243193136819,174.81055181552267</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>-36.82484351939028,174.81118954153368</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>-36.819511011006824,174.80658221291824</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>-36.82013929619381,174.80702424088645</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>-36.820716147727076,174.80755643864347</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>-36.82131403968895,174.80807111067944</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>-36.8219035839384,174.8085882826184</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>-36.82249094849653,174.80910921094878</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>-36.8230914557875,174.8096076578231</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>-36.823730200368324,174.81003284087646</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>-36.824324875819,174.8105416088673</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>-36.82484917070752,174.81118154214678</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>-36.819510817265424,174.80658259101222</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>-36.82013997377726,174.8070229171419</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>-36.820717262858466,174.80755413359134</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>-36.82131403968895,174.80807111067944</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>-36.82190402714015,174.80858743772393</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>-36.82249089943036,174.8091093049711</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>-36.823092257853546,174.80960616739983</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>-36.82373085205143,174.81003162990152</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>-36.824325684857065,174.81054012426276</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>-36.82485047943355,174.81117968965702</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
